--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487541_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487541_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.871</v>
+        <v>5.8967</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3848</v>
+        <v>6.1966</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5138</v>
+        <v>-0.2999</v>
       </c>
       <c r="G2" t="n">
         <v>3.2933</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6819</v>
+        <v>0.7075</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6693</v>
+        <v>0.4811</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0126</v>
+        <v>0.2264</v>
       </c>
       <c r="V2" t="n">
         <v>0.1332</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9359</v>
+        <v>2.1454</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1255</v>
+        <v>3.2013</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1895</v>
+        <v>-1.0559</v>
       </c>
       <c r="G3" t="n">
         <v>2.9218</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5273</v>
+        <v>0.7368</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3482</v>
+        <v>0.424</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1791</v>
+        <v>0.3127</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1422</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1288</v>
+        <v>1.0768</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4514</v>
+        <v>-0.5568</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5802</v>
+        <v>1.6337</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8216</v>
@@ -766,13 +766,13 @@
         <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8072</v>
+        <v>0.1409</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9745</v>
+        <v>-0.08</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1674</v>
+        <v>0.2209</v>
       </c>
       <c r="V4" t="n">
         <v>0.1908</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.652</v>
+        <v>-0.5985</v>
       </c>
       <c r="E5" t="n">
         <v>-1.1356</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4836</v>
+        <v>0.5371</v>
       </c>
       <c r="G5" t="n">
         <v>0.1552</v>
@@ -844,13 +844,13 @@
         <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6113</v>
+        <v>-0.5578</v>
       </c>
       <c r="T5" t="n">
         <v>-0.2376</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3737</v>
+        <v>-0.3202</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>R. SANCHEZ PARRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7129</v>
+        <v>-0.6422</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6143999999999999</v>
+        <v>-0.5147</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3272</v>
+        <v>-0.1275</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.2306</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0837</v>
+        <v>-0.1225</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.1468</v>
+        <v>-0.8135</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2703</v>
+        <v>-0.6006</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0683</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2021</v>
+        <v>-0.6822</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.5009</v>
+        <v>-0.3354</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.152</v>
+        <v>-0.2042</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.3489</v>
+        <v>-0.1313</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9585</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7946</v>
+        <v>0.2938</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7126</v>
+        <v>0.0859</v>
       </c>
       <c r="U6" t="n">
-        <v>1.082</v>
+        <v>0.2079</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2562</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.3894</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. SANCHEZ PARRES</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7934</v>
+        <v>-1.8091</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7194</v>
+        <v>-0.1878</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.074</v>
+        <v>-1.6213</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-3.2306</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1225</v>
+        <v>-0.0837</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8135</v>
+        <v>-3.1468</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6006</v>
+        <v>1.2703</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08169999999999999</v>
+        <v>1.0683</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6822</v>
+        <v>0.2021</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3354</v>
+        <v>-4.5009</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2042</v>
+        <v>-1.152</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1313</v>
+        <v>-3.3489</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.9585</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1426</v>
+        <v>1.6984</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1188</v>
+        <v>0.9104</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2614</v>
+        <v>0.788</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2562</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-1.3894</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.1332</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8216</v>
+        <v>-1.8171</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6055</v>
+        <v>-0.7078</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2161</v>
+        <v>-1.1092</v>
       </c>
       <c r="G8" t="n">
         <v>-2.1417</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1242</v>
+        <v>0.1288</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4623</v>
+        <v>0.3599</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3381</v>
+        <v>-0.2311</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4598</v>
+        <v>-3.0861</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.959</v>
+        <v>-2.3715</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5008</v>
+        <v>-0.7147</v>
       </c>
       <c r="G10" t="n">
         <v>-4.2018</v>
@@ -1234,13 +1234,13 @@
         <v>2.546</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1544</v>
+        <v>0.5281</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3517</v>
+        <v>0.2358</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5062</v>
+        <v>0.2923</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1374</v>
+        <v>-4.9162</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7231</v>
+        <v>-3.5019</v>
       </c>
       <c r="F11" t="n">
         <v>-1.4143</v>
@@ -1312,10 +1312,10 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1429</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4705</v>
+        <v>-0.2494</v>
       </c>
       <c r="U11" t="n">
         <v>0.3276</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.503699999999998</v>
+        <v>-6.6126</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4878999999999989</v>
+        <v>0.4032</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.0156</v>
+        <v>-7.0157</v>
       </c>
       <c r="G12" t="n">
         <v>-13.8276</v>
@@ -1390,10 +1390,10 @@
         <v>14.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2906</v>
+        <v>4.1817</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3234</v>
+        <v>2.2142</v>
       </c>
       <c r="U12" t="n">
         <v>1.9674</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9697</v>
+        <v>7.5257</v>
       </c>
       <c r="E13" t="n">
-        <v>7.3348</v>
+        <v>7.6418</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3651</v>
+        <v>-0.1161</v>
       </c>
       <c r="G13" t="n">
         <v>7.806</v>
@@ -1468,13 +1468,13 @@
         <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2867</v>
+        <v>-0.7308</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0933</v>
+        <v>-0.7863</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1934</v>
+        <v>0.0556</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3329</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2585</v>
+        <v>3.3425</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8707</v>
+        <v>1.973</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3878</v>
+        <v>1.3695</v>
       </c>
       <c r="G14" t="n">
         <v>3.135</v>
@@ -1546,13 +1546,13 @@
         <v>2.1543</v>
       </c>
       <c r="S14" t="n">
-        <v>0.203</v>
+        <v>0.287</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2923</v>
+        <v>-0.19</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4953</v>
+        <v>0.477</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2754</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0956</v>
+        <v>2.9695</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7516</v>
+        <v>3.0586</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.656</v>
+        <v>-0.0891</v>
       </c>
       <c r="G15" t="n">
         <v>4.7192</v>
@@ -1624,13 +1624,13 @@
         <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7031</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6775</v>
+        <v>-0.3705</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0255</v>
+        <v>-0.4586</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3329</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9403</v>
+        <v>1.3622</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2963</v>
+        <v>0.4209</v>
       </c>
       <c r="F16" t="n">
-        <v>0.644</v>
+        <v>0.9413</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2338</v>
+        <v>3.2271</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7091</v>
+        <v>-0.2341</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4753</v>
+        <v>3.4612</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2963</v>
+        <v>4.4865</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3675</v>
+        <v>1.7334</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0712</v>
+        <v>2.753</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0625</v>
+        <v>-1.2594</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3416</v>
+        <v>-1.9676</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4042</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3917</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3917</v>
+        <v>1.9585</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3148</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.3088</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3148</v>
+        <v>0.2422</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1602</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1602</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6099</v>
+        <v>1.1717</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3186</v>
+        <v>0.501</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2914</v>
+        <v>0.6707</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2271</v>
+        <v>0.2338</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2341</v>
+        <v>0.7091</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4612</v>
+        <v>-0.4753</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4865</v>
+        <v>0.2963</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7334</v>
+        <v>0.3675</v>
       </c>
       <c r="L17" t="n">
-        <v>2.753</v>
+        <v>-0.0712</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2594</v>
+        <v>-0.0625</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9676</v>
+        <v>0.3416</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7082000000000001</v>
+        <v>-0.4042</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9585</v>
+        <v>0.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9585</v>
+        <v>0.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8189</v>
+        <v>0.5462</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4111</v>
+        <v>0.2047</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4077</v>
+        <v>0.3416</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1602</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1602</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0582</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E18" t="n">
         <v>0.0404</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="G18" t="n">
         <v>0.0404</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4469</v>
+        <v>-1.0388</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1469</v>
+        <v>-0.7741</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5938</v>
+        <v>-0.2647</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5857</v>
@@ -1936,13 +1936,13 @@
         <v>1.5668</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4153</v>
+        <v>-0.1766</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2921</v>
+        <v>0.3711</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8768</v>
+        <v>-0.5477</v>
       </c>
       <c r="V19" t="n">
         <v>0.1152</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>S. MUJICA LANDAETA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6866</v>
+        <v>-1.708</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.116</v>
+        <v>-2.7533</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5707</v>
+        <v>1.0453</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1698</v>
+        <v>-0.5998</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8717</v>
+        <v>-1.4893</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2981</v>
+        <v>0.8895</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5595</v>
+        <v>-0.3373</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6499</v>
+        <v>-0.5393</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0905</v>
+        <v>0.2021</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6104</v>
+        <v>-0.2625</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2218</v>
+        <v>-0.9499</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3886</v>
+        <v>0.6874</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9792</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0295</v>
+        <v>0.2051</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.09</v>
+        <v>-0.4576</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0605</v>
+        <v>0.6627</v>
       </c>
       <c r="V20" t="n">
-        <v>1.492</v>
+        <v>0.0576</v>
       </c>
       <c r="W20" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MUJICA LANDAETA</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8417</v>
+        <v>-1.7595</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7533</v>
+        <v>-1.2183</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9117</v>
+        <v>-0.5411</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5998</v>
+        <v>-2.1698</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4893</v>
+        <v>-1.8717</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8895</v>
+        <v>-0.2981</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3373</v>
+        <v>-0.5595</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5393</v>
+        <v>-0.6499</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2021</v>
+        <v>0.0905</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2625</v>
+        <v>-1.6104</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9499</v>
+        <v>-1.2218</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6874</v>
+        <v>-0.3886</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3709</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>0.07149999999999999</v>
+        <v>-0.1023</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4576</v>
+        <v>-0.1923</v>
       </c>
       <c r="U21" t="n">
-        <v>0.529</v>
+        <v>0.09</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0576</v>
+        <v>1.492</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4535</v>
+        <v>-2.4</v>
       </c>
       <c r="E22" t="n">
         <v>-1.5412</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9122</v>
+        <v>-0.8588</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9786</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4749</v>
+        <v>-0.4214</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2376</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2373</v>
+        <v>-0.1838</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.503499999999999</v>
+        <v>9.550299999999998</v>
       </c>
       <c r="E23" t="n">
         <v>7.348800000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1548999999999999</v>
+        <v>2.2016</v>
       </c>
       <c r="G23" t="n">
         <v>13.8276</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.093400000000001</v>
+        <v>-5.093399999999999</v>
       </c>
       <c r="I23" t="n">
         <v>18.9209</v>
@@ -2224,13 +2224,13 @@
         <v>22.1348</v>
       </c>
       <c r="K23" t="n">
-        <v>6.0986</v>
+        <v>6.098599999999999</v>
       </c>
       <c r="L23" t="n">
         <v>16.0362</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.3072</v>
+        <v>-8.307200000000002</v>
       </c>
       <c r="N23" t="n">
         <v>-11.1919</v>
@@ -2248,22 +2248,22 @@
         <v>10.7715</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.2907</v>
+        <v>-1.2439</v>
       </c>
       <c r="T23" t="n">
         <v>-1.9673</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3233</v>
+        <v>0.7235999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8837999999999999</v>
+        <v>0.8838000000000001</v>
       </c>
       <c r="W23" t="n">
         <v>1.87</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9863000000000001</v>
+        <v>-0.9863</v>
       </c>
     </row>
   </sheetData>
